--- a/Data/Building/Context.UltravioletLevel.xlsx
+++ b/Data/Building/Context.UltravioletLevel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:I217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709234758</v>
+        <v>1711827689</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709251978</v>
+        <v>1711844081</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709258692</v>
+        <v>1711851124</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709264938</v>
+        <v>1711857827</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709268830</v>
+        <v>1711861148</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709275446</v>
+        <v>1711867493</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709277213</v>
+        <v>1711869119</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709277715</v>
+        <v>1711869560</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709243094</v>
+        <v>1711910545</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709250269</v>
+        <v>1711924227</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709255986</v>
+        <v>1711930023</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709263309</v>
+        <v>1711935259</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +865,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709267578</v>
+        <v>1711938762</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +898,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709268354</v>
+        <v>1711944404</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +931,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709318746</v>
+        <v>1711945640</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709332022</v>
+        <v>1711945971</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +997,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709338383</v>
+        <v>1712008108</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1030,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709345724</v>
+        <v>1712016573</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1063,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709349603</v>
+        <v>1712022233</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709355933</v>
+        <v>1712029775</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709357133</v>
+        <v>1712034533</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709357730</v>
+        <v>1712035375</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709403481</v>
+        <v>1712083965</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709417274</v>
+        <v>1712097786</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709423459</v>
+        <v>1712104231</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1298,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709430159</v>
+        <v>1712111999</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1331,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709433788</v>
+        <v>1712116455</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1364,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709440392</v>
+        <v>1712123461</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1397,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709442121</v>
+        <v>1712124607</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1430,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709442611</v>
+        <v>1712125244</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709499529</v>
+        <v>1712169267</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1496,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709508183</v>
+        <v>1712181700</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1529,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709513648</v>
+        <v>1712187870</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709521736</v>
+        <v>1712194888</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1591,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709526699</v>
+        <v>1712199168</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1624,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709527704</v>
+        <v>1712206294</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1657,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709577499</v>
+        <v>1712208265</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1694,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709591332</v>
+        <v>1712208811</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1723,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709597782</v>
+        <v>1712264440</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1756,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709605362</v>
+        <v>1712271856</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1789,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709608770</v>
+        <v>1712277683</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1826,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709615677</v>
+        <v>1712285576</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1859,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709616780</v>
+        <v>1712290871</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1892,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709617397</v>
+        <v>1712291740</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1925,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709664360</v>
+        <v>1712343397</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1958,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709678107</v>
+        <v>1712356738</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +1991,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709685089</v>
+        <v>1712363727</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2024,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709693554</v>
+        <v>1712371687</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2057,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709698666</v>
+        <v>1712377784</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2090,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709707281</v>
+        <v>1712386751</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709709379</v>
+        <v>1712389249</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2156,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709710075</v>
+        <v>1712390191</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2189,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709761253</v>
+        <v>1712430354</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709770623</v>
+        <v>1712444161</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2255,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709777383</v>
+        <v>1712451888</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2288,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709785933</v>
+        <v>1712460674</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2257,10 +2317,11 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709791998</v>
+        <v>1712465006</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2350,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709793224</v>
+        <v>1712474041</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2383,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709836657</v>
+        <v>1712476558</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2420,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709849396</v>
+        <v>1712477296</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2449,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709854622</v>
+        <v>1712516834</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2482,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2505,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709860882</v>
+        <v>1712530128</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2515,11 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2538,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709864506</v>
+        <v>1712535871</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2552,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2571,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709870244</v>
+        <v>1712543091</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2581,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2604,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709871271</v>
+        <v>1712546746</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2614,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2637,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709871876</v>
+        <v>1712552376</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2647,11 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2670,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709923170</v>
+        <v>1712553390</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2684,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2703,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709936485</v>
+        <v>1712553960</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2713,11 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2736,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709941853</v>
+        <v>1712601212</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2746,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2769,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709948304</v>
+        <v>1712615439</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2779,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2802,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709951820</v>
+        <v>1712621562</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2816,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2835,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709958030</v>
+        <v>1712628225</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2845,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2868,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709959829</v>
+        <v>1712631794</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2801,10 +2878,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2901,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709960167</v>
+        <v>1712637540</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2833,10 +2911,11 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2934,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710010028</v>
+        <v>1712638567</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2948,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2967,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710024212</v>
+        <v>1712639098</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +2977,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3000,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710030657</v>
+        <v>1712701752</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2929,10 +3010,11 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3033,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710037399</v>
+        <v>1712709725</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3043,11 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3066,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710041670</v>
+        <v>1712714965</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3080,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3099,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710048505</v>
+        <v>1712722102</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3113,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3132,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710050046</v>
+        <v>1712726588</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3146,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710050651</v>
+        <v>1712727460</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3179,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3198,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710097013</v>
+        <v>1712775829</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3212,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3231,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710111030</v>
+        <v>1712790543</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3245,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3264,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710117466</v>
+        <v>1712797105</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3278,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3297,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710124928</v>
+        <v>1712803031</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3311,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3330,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710128670</v>
+        <v>1712806204</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3344,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3363,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710135092</v>
+        <v>1712811108</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3377,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3396,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710136634</v>
+        <v>1712812573</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3410,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3429,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710137239</v>
+        <v>1712812949</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3443,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3462,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710181511</v>
+        <v>1712860922</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3476,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3495,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710195490</v>
+        <v>1712875171</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3509,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3528,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710202235</v>
+        <v>1712881669</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3542,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3561,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710208641</v>
+        <v>1712888365</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3575,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3594,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710213648</v>
+        <v>1712891189</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3608,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3627,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710220495</v>
+        <v>1712897484</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3641,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3660,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710222581</v>
+        <v>1712898449</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3674,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3693,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710223268</v>
+        <v>1712899261</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3707,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3726,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710268285</v>
+        <v>1712946123</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3740,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3759,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710281597</v>
+        <v>1712959690</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3773,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3792,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710289127</v>
+        <v>1712967517</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3806,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3825,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710297537</v>
+        <v>1712976309</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3839,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3858,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710302092</v>
+        <v>1712980531</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3872,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3891,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710311174</v>
+        <v>1712988388</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3905,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3924,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710313918</v>
+        <v>1712990306</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3938,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3957,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710314857</v>
+        <v>1712991156</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +3971,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +3990,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710365466</v>
+        <v>1713034460</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4004,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4023,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710375747</v>
+        <v>1713047760</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4037,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4056,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710383296</v>
+        <v>1713055535</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4070,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4089,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710392881</v>
+        <v>1713064266</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4099,11 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4122,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710399735</v>
+        <v>1713069518</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4132,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4155,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710401034</v>
+        <v>1713077917</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4165,11 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4188,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710441758</v>
+        <v>1713079452</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4202,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4221,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710455699</v>
+        <v>1713080106</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4231,11 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4254,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710461628</v>
+        <v>1713129748</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4264,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4287,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710467849</v>
+        <v>1713137326</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4177,10 +4297,11 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4320,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710470972</v>
+        <v>1713142351</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4334,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4353,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710476964</v>
+        <v>1713149682</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4367,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4386,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710478843</v>
+        <v>1713154560</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4400,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4419,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710479542</v>
+        <v>1713155412</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4433,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4452,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710527292</v>
+        <v>1713206492</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4466,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4485,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710540733</v>
+        <v>1713219251</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4499,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4518,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710546192</v>
+        <v>1713224797</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4532,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4551,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710552884</v>
+        <v>1713231050</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4565,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4584,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710557068</v>
+        <v>1713235261</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4598,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4617,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710563280</v>
+        <v>1713240762</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4631,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4650,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710564698</v>
+        <v>1713241558</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4664,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4683,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710565068</v>
+        <v>1713242002</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4697,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4716,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710615243</v>
+        <v>1713293563</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4730,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4749,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710629422</v>
+        <v>1713306584</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4763,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4782,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710635616</v>
+        <v>1713312121</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4796,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4815,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710642669</v>
+        <v>1713318593</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4829,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4848,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710646059</v>
+        <v>1713321793</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4862,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4881,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710652235</v>
+        <v>1713326570</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4895,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4914,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710653514</v>
+        <v>1713327492</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4928,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4947,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710654035</v>
+        <v>1713327927</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +4961,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +4980,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710700195</v>
+        <v>1713388530</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +4994,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5013,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710714326</v>
+        <v>1713395549</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5027,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5046,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710720247</v>
+        <v>1713400306</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5060,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5079,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710726889</v>
+        <v>1713406656</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4945,10 +5089,11 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5112,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710730042</v>
+        <v>1713411119</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5122,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5145,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710736182</v>
+        <v>1713411960</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5009,10 +5155,11 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5178,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710737106</v>
+        <v>1713465633</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5192,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5211,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710737719</v>
+        <v>1713479503</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5221,11 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5244,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710787299</v>
+        <v>1713485938</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5254,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5277,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710801312</v>
+        <v>1713491518</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5137,10 +5287,11 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5310,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710807495</v>
+        <v>1713494821</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5324,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5343,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710814058</v>
+        <v>1713499864</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5201,10 +5353,11 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5376,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710817975</v>
+        <v>1713500913</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5386,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5409,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710824540</v>
+        <v>1713501308</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5265,10 +5419,11 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5442,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710826085</v>
+        <v>1713552490</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5456,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5475,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710826661</v>
+        <v>1713565855</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5485,11 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5508,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710873840</v>
+        <v>1713572621</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5518,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5541,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710887248</v>
+        <v>1713579902</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5393,10 +5551,11 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5574,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710894943</v>
+        <v>1713584098</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5588,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5607,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710903836</v>
+        <v>1713591025</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5617,11 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5640,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710909359</v>
+        <v>1713592733</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5489,10 +5650,11 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5673,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710918088</v>
+        <v>1713593517</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5521,10 +5683,11 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5706,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710919979</v>
+        <v>1713637072</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5720,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5739,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710920892</v>
+        <v>1713650954</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5585,10 +5749,11 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5772,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710960914</v>
+        <v>1713658629</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +5782,11 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5805,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710974770</v>
+        <v>1713667167</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5815,11 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5838,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710982366</v>
+        <v>1713671397</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5852,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5871,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710990829</v>
+        <v>1713679495</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5713,10 +5881,11 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5904,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710996306</v>
+        <v>1713681637</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +5914,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +5937,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711004658</v>
+        <v>1713682304</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5777,10 +5947,11 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +5970,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711007359</v>
+        <v>1713725331</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +5984,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6003,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711008049</v>
+        <v>1713738258</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5841,10 +6013,11 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6036,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711057153</v>
+        <v>1713744165</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5873,10 +6046,11 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6069,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711064659</v>
+        <v>1713750127</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5905,10 +6079,11 @@
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6102,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711070603</v>
+        <v>1713753705</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6116,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6135,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711078172</v>
+        <v>1713759530</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6149,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6168,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711083481</v>
+        <v>1713761027</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6182,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6201,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711084508</v>
+        <v>1713761947</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6215,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6234,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711133107</v>
+        <v>1713821021</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6248,7 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6267,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711146748</v>
+        <v>1713829357</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6281,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6300,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711152516</v>
+        <v>1713835135</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6314,7 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6333,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711159066</v>
+        <v>1713842908</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6343,11 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6366,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711162881</v>
+        <v>1713847694</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6193,10 +6376,11 @@
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6399,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711170087</v>
+        <v>1713848426</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6225,10 +6409,11 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6432,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1711171590</v>
+        <v>1713897508</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6446,7 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6465,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1711172153</v>
+        <v>1713911100</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6289,10 +6475,11 @@
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6498,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1711219407</v>
+        <v>1713917200</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6321,10 +6508,11 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6531,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1711232779</v>
+        <v>1713923798</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6353,10 +6541,11 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6564,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1711238213</v>
+        <v>1713927908</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6578,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6597,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1711245088</v>
+        <v>1713933647</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6417,10 +6607,11 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6630,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1711249424</v>
+        <v>1713935924</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6449,10 +6640,11 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6663,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711256079</v>
+        <v>1713936478</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6481,10 +6673,11 @@
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6696,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711257952</v>
+        <v>1713993057</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6710,7 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6729,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711258650</v>
+        <v>1713999897</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6545,10 +6739,11 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6762,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711306878</v>
+        <v>1714003576</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6577,10 +6772,11 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6795,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711319516</v>
+        <v>1714010528</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6613,6 +6809,7 @@
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6828,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711325154</v>
+        <v>1714015065</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6641,10 +6838,11 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6861,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711331476</v>
+        <v>1714016008</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6673,10 +6871,11 @@
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6894,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711335419</v>
+        <v>1714080341</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6705,10 +6904,11 @@
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +6927,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711341194</v>
+        <v>1714087379</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6741,6 +6941,7 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +6960,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711342901</v>
+        <v>1714091589</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6769,10 +6970,11 @@
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +6993,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711343543</v>
+        <v>1714097899</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6801,10 +7003,11 @@
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7026,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711391773</v>
+        <v>1714102171</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7040,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7059,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711405539</v>
+        <v>1714102971</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6865,10 +7069,11 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7092,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711412111</v>
+        <v>1714157203</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6897,10 +7102,11 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7125,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711418751</v>
+        <v>1714170127</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6929,10 +7135,11 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7158,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711422416</v>
+        <v>1714177253</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7172,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7191,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711429003</v>
+        <v>1714184837</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6993,10 +7201,11 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7224,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711430433</v>
+        <v>1714188600</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7025,10 +7234,11 @@
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7257,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711430960</v>
+        <v>1714196767</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7057,10 +7267,11 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7290,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711479529</v>
+        <v>1714198590</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7304,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7323,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711493745</v>
+        <v>1714199279</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7121,10 +7333,11 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7356,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711501234</v>
+        <v>1714242858</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7153,10 +7366,11 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7389,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711509919</v>
+        <v>1714256439</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7185,10 +7399,11 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7422,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1711514213</v>
+        <v>1714263374</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7436,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7455,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1711522908</v>
+        <v>1714271593</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7249,10 +7465,11 @@
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7488,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1711525372</v>
+        <v>1714275697</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7281,10 +7498,11 @@
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7521,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1711526051</v>
+        <v>1714283360</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7313,10 +7531,11 @@
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7554,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1711566287</v>
+        <v>1714285077</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7568,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7587,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1711580520</v>
+        <v>1714285772</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7377,202 +7597,11 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>1711588259</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>1711597694</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>1711602257</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>1711610647</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>1711613012</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>1711613884</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
